--- a/education_forms/049_graduate_student_application_form--education_forms.xlsx
+++ b/education_forms/049_graduate_student_application_form--education_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -834,8 +834,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
-    <col width="29" customWidth="1" min="2" max="2"/>
-    <col width="29" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -863,12 +863,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'in_progress'}</t>
+          <t>in_progress</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'In Progress'}</t>
+          <t>In Progress</t>
         </is>
       </c>
     </row>
@@ -880,12 +880,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'completed'}</t>
+          <t>completed</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': 'Completed'}</t>
+          <t>Completed</t>
         </is>
       </c>
     </row>
@@ -897,12 +897,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'deferred'}</t>
+          <t>deferred</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'Deferred'}</t>
+          <t>Deferred</t>
         </is>
       </c>
     </row>
@@ -914,12 +914,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'denied'}</t>
+          <t>denied</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'Denied'}</t>
+          <t>Denied</t>
         </is>
       </c>
     </row>
@@ -931,12 +931,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'master'}</t>
+          <t>master</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'Master'}</t>
+          <t>Master</t>
         </is>
       </c>
     </row>
@@ -948,12 +948,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'phd'}</t>
+          <t>phd</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'PhD'}</t>
+          <t>PhD</t>
         </is>
       </c>
     </row>
@@ -965,12 +965,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'certificate'}</t>
+          <t>certificate</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': 'Certificate'}</t>
+          <t>Certificate</t>
         </is>
       </c>
     </row>
@@ -982,12 +982,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'bachelor'}</t>
+          <t>bachelor</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': 'Bachelor'}</t>
+          <t>Bachelor</t>
         </is>
       </c>
     </row>
@@ -999,12 +999,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_'master'}</t>
+          <t>master</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': 'Master'}</t>
+          <t>Master</t>
         </is>
       </c>
     </row>
@@ -1016,12 +1016,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'label':_'doctoral'}</t>
+          <t>doctoral</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'label': 'Doctoral'}</t>
+          <t>Doctoral</t>
         </is>
       </c>
     </row>
@@ -1033,12 +1033,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'label':_'in_progress'}</t>
+          <t>in_progress</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'label': 'In Progress'}</t>
+          <t>In Progress</t>
         </is>
       </c>
     </row>
@@ -1050,12 +1050,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'label':_'completed'}</t>
+          <t>completed</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'label': 'Completed'}</t>
+          <t>Completed</t>
         </is>
       </c>
     </row>
@@ -1067,12 +1067,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'label':_'withdrawn'}</t>
+          <t>withdrawn</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'label': 'Withdrawn'}</t>
+          <t>Withdrawn</t>
         </is>
       </c>
     </row>
@@ -1084,12 +1084,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'label':_'submit'}</t>
+          <t>submit</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'label': 'Submit'}</t>
+          <t>Submit</t>
         </is>
       </c>
     </row>
@@ -1101,12 +1101,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'label':_'save_for_later'}</t>
+          <t>save_for_later</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'label': 'Save for Later'}</t>
+          <t>Save for Later</t>
         </is>
       </c>
     </row>
@@ -1118,12 +1118,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'label':_'cancel'}</t>
+          <t>cancel</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'label': 'Cancel'}</t>
+          <t>Cancel</t>
         </is>
       </c>
     </row>
